--- a/ARM Functions/Other Mechanics/Weather chip and power and stat mods.xlsx
+++ b/ARM Functions/Other Mechanics/Weather chip and power and stat mods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BE8F79-8753-4CAC-A93A-7B7E12DFDCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427F2CEB-47A1-4803-A3EF-AE2F4B0746C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Edited main" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="126">
   <si>
     <t>Address</t>
   </si>
@@ -412,13 +412,16 @@
   </si>
   <si>
     <t>FB88FC0A</t>
+  </si>
+  <si>
+    <t>Saves pointer to Pokemon in r4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -524,8 +527,6 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -861,18 +862,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD17F403-0334-4F0F-BD62-1976F89E9C58}">
   <dimension ref="A1:F125"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="9.35546875" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.265625" customWidth="1"/>
-    <col min="5" max="5" width="3.59765625" customWidth="1"/>
-    <col min="6" max="6" width="12.73046875" customWidth="1"/>
-    <col min="7" max="7" width="13.59765625" customWidth="1"/>
+    <col min="3" max="3" width="16.640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.28515625" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -886,7 +887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
         <v>39</v>
       </c>
@@ -894,7 +895,7 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -905,7 +906,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" s="19" t="str">
         <f>DEC2HEX(HEX2DEC(A3)+4,8)</f>
         <v>000B0504</v>
@@ -920,20 +921,22 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="19" t="str">
+    <row r="5" spans="1:6">
+      <c r="A5" s="25" t="str">
         <f t="shared" ref="A5:A58" si="0">DEC2HEX(HEX2DEC(A4)+4,8)</f>
         <v>000B0508</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="19"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D5" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="19" t="str">
         <f t="shared" si="0"/>
         <v>000B050C</v>
@@ -946,7 +949,7 @@
       </c>
       <c r="D6" s="19"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>000B0510</v>
@@ -961,7 +964,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="A8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>000B0514</v>
@@ -974,7 +977,7 @@
       </c>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6">
       <c r="A9" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0518</v>
@@ -989,7 +992,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6">
       <c r="A10" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B051C</v>
@@ -1002,7 +1005,7 @@
       </c>
       <c r="D10" s="15"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6">
       <c r="A11" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0520</v>
@@ -1015,7 +1018,7 @@
       </c>
       <c r="D11" s="15"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6">
       <c r="A12" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0524</v>
@@ -1028,7 +1031,7 @@
       </c>
       <c r="D12" s="15"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6">
       <c r="A13" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0528</v>
@@ -1041,7 +1044,7 @@
       </c>
       <c r="D13" s="15"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6">
       <c r="A14" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B052C</v>
@@ -1054,7 +1057,7 @@
       </c>
       <c r="D14" s="15"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6">
       <c r="A15" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0530</v>
@@ -1068,7 +1071,7 @@
       <c r="D15" s="15"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6">
       <c r="A16" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0534</v>
@@ -1081,7 +1084,7 @@
       </c>
       <c r="D16" s="15"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6">
       <c r="A17" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0538</v>
@@ -1094,7 +1097,7 @@
       </c>
       <c r="D17" s="15"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6">
       <c r="A18" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B053C</v>
@@ -1107,7 +1110,7 @@
       </c>
       <c r="D18" s="15"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6">
       <c r="A19" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0540</v>
@@ -1120,7 +1123,7 @@
       </c>
       <c r="D19" s="15"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6">
       <c r="A20" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0544</v>
@@ -1134,7 +1137,7 @@
       <c r="D20" s="16"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6">
       <c r="A21" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0548</v>
@@ -1147,7 +1150,7 @@
       </c>
       <c r="D21" s="16"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6">
       <c r="A22" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B054C</v>
@@ -1160,7 +1163,7 @@
       </c>
       <c r="D22" s="16"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6">
       <c r="A23" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0550</v>
@@ -1173,7 +1176,7 @@
       </c>
       <c r="D23" s="16"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6">
       <c r="A24" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000B0554</v>
@@ -1188,7 +1191,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6">
       <c r="A25" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000B0558</v>
@@ -1201,7 +1204,7 @@
       </c>
       <c r="D25" s="5"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6">
       <c r="A26" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000B055C</v>
@@ -1214,7 +1217,7 @@
       </c>
       <c r="D26" s="5"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6">
       <c r="A27" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000B0560</v>
@@ -1227,7 +1230,7 @@
       </c>
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6">
       <c r="A28" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000B0564</v>
@@ -1240,7 +1243,7 @@
       </c>
       <c r="D28" s="5"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6">
       <c r="A29" s="6" t="str">
         <f t="shared" si="0"/>
         <v>000B0568</v>
@@ -1255,7 +1258,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6">
       <c r="A30" s="6" t="str">
         <f t="shared" si="0"/>
         <v>000B056C</v>
@@ -1268,7 +1271,7 @@
       </c>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6">
       <c r="A31" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0570</v>
@@ -1283,7 +1286,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6">
       <c r="A32" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0574</v>
@@ -1296,7 +1299,7 @@
       </c>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4">
       <c r="A33" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0578</v>
@@ -1309,7 +1312,7 @@
       </c>
       <c r="D33" s="13"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4">
       <c r="A34" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B057C</v>
@@ -1322,7 +1325,7 @@
       </c>
       <c r="D34" s="13"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4">
       <c r="A35" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0580</v>
@@ -1335,7 +1338,7 @@
       </c>
       <c r="D35" s="13"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4">
       <c r="A36" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0584</v>
@@ -1348,7 +1351,7 @@
       </c>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4">
       <c r="A37" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0588</v>
@@ -1361,7 +1364,7 @@
       </c>
       <c r="D37" s="13"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4">
       <c r="A38" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B058C</v>
@@ -1374,7 +1377,7 @@
       </c>
       <c r="D38" s="13"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4">
       <c r="A39" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0590</v>
@@ -1387,18 +1390,18 @@
       </c>
       <c r="D39" s="13"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4">
       <c r="B40" s="2"/>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4">
       <c r="A41" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B41" s="3"/>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>71</v>
       </c>
@@ -1410,7 +1413,7 @@
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4">
       <c r="A43" t="str">
         <f t="shared" si="0"/>
         <v>0001FA28</v>
@@ -1425,7 +1428,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4">
       <c r="A44" t="str">
         <f t="shared" si="0"/>
         <v>0001FA2C</v>
@@ -1441,7 +1444,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4">
       <c r="A45" t="str">
         <f t="shared" si="0"/>
         <v>0001FA30</v>
@@ -1454,7 +1457,7 @@
       </c>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4">
       <c r="A46" t="str">
         <f t="shared" si="0"/>
         <v>0001FA34</v>
@@ -1467,7 +1470,7 @@
       </c>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4">
       <c r="A47" s="8" t="str">
         <f t="shared" si="0"/>
         <v>0001FA38</v>
@@ -1482,7 +1485,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4">
       <c r="A48" s="8" t="str">
         <f t="shared" si="0"/>
         <v>0001FA3C</v>
@@ -1495,7 +1498,7 @@
       </c>
       <c r="D48" s="22"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4">
       <c r="A49" s="8" t="str">
         <f t="shared" si="0"/>
         <v>0001FA40</v>
@@ -1508,7 +1511,7 @@
       </c>
       <c r="D49" s="22"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4">
       <c r="A50" s="19" t="str">
         <f t="shared" si="0"/>
         <v>0001FA44</v>
@@ -1523,7 +1526,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4">
       <c r="A51" s="19" t="str">
         <f t="shared" si="0"/>
         <v>0001FA48</v>
@@ -1536,7 +1539,7 @@
       </c>
       <c r="D51" s="24"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4">
       <c r="A52" s="19" t="str">
         <f t="shared" si="0"/>
         <v>0001FA4C</v>
@@ -1549,7 +1552,7 @@
       </c>
       <c r="D52" s="24"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4">
       <c r="A53" s="15" t="str">
         <f t="shared" si="0"/>
         <v>0001FA50</v>
@@ -1564,7 +1567,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4">
       <c r="A54" s="15" t="str">
         <f t="shared" si="0"/>
         <v>0001FA54</v>
@@ -1577,7 +1580,7 @@
       </c>
       <c r="D54" s="17"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4">
       <c r="A55" t="str">
         <f t="shared" si="0"/>
         <v>0001FA58</v>
@@ -1592,7 +1595,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4">
       <c r="A56" t="str">
         <f t="shared" si="0"/>
         <v>0001FA5C</v>
@@ -1607,7 +1610,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4">
       <c r="A57" t="str">
         <f t="shared" si="0"/>
         <v>0001FA60</v>
@@ -1622,7 +1625,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4">
       <c r="A58" t="str">
         <f t="shared" si="0"/>
         <v>0001FA64</v>
@@ -1637,18 +1640,18 @@
         <v>102</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4">
       <c r="B59" s="2"/>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4">
       <c r="A60" s="4" t="s">
         <v>103</v>
       </c>
       <c r="B60" s="2"/>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -1662,7 +1665,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4">
       <c r="A62" t="str">
         <f t="shared" ref="A62:A72" si="1">DEC2HEX(HEX2DEC(A61)+4,8)</f>
         <v>000FD658</v>
@@ -1678,7 +1681,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:4">
       <c r="A63" t="str">
         <f t="shared" si="1"/>
         <v>000FD65C</v>
@@ -1693,7 +1696,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:4">
       <c r="A64" t="str">
         <f t="shared" si="1"/>
         <v>000FD660</v>
@@ -1706,7 +1709,7 @@
       </c>
       <c r="D64" s="2"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4">
       <c r="A65" t="str">
         <f t="shared" si="1"/>
         <v>000FD664</v>
@@ -1721,7 +1724,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4">
       <c r="A66" t="str">
         <f t="shared" si="1"/>
         <v>000FD668</v>
@@ -1734,7 +1737,7 @@
       </c>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4">
       <c r="A67" t="str">
         <f t="shared" si="1"/>
         <v>000FD66C</v>
@@ -1746,7 +1749,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4">
       <c r="A68" t="str">
         <f t="shared" si="1"/>
         <v>000FD670</v>
@@ -1759,20 +1762,20 @@
       </c>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="25" t="str">
+    <row r="69" spans="1:4">
+      <c r="A69" t="str">
         <f t="shared" si="1"/>
         <v>000FD674</v>
       </c>
-      <c r="B69" s="26" t="s">
+      <c r="B69" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" t="s">
         <v>123</v>
       </c>
-      <c r="D69" s="27"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D69" s="2"/>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" t="str">
         <f t="shared" si="1"/>
         <v>000FD678</v>
@@ -1787,7 +1790,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4">
       <c r="A71" t="str">
         <f t="shared" si="1"/>
         <v>000FD67C</v>
@@ -1800,7 +1803,7 @@
       </c>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4">
       <c r="A72" t="str">
         <f t="shared" si="1"/>
         <v>000FD680</v>
@@ -1814,72 +1817,72 @@
       </c>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4">
       <c r="B73" s="2"/>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4">
       <c r="B74" s="2"/>
       <c r="D74" s="3"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4">
       <c r="B75" s="2"/>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:4">
       <c r="B76" s="2"/>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:4">
       <c r="B77" s="2"/>
       <c r="D77" s="2"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:4">
       <c r="B78" s="2"/>
       <c r="D78" s="2"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4">
       <c r="B79" s="2"/>
       <c r="D79" s="2"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:2">
       <c r="B81" s="1"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:2">
       <c r="B86" s="1"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:2">
       <c r="B88" s="1"/>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:2">
       <c r="B91" s="1"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:2">
       <c r="B92" s="1"/>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:2">
       <c r="B93" s="1"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:4">
       <c r="B98" s="1"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:4">
       <c r="B102" s="1"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:4">
       <c r="B106" s="1"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:4">
       <c r="A107" s="4"/>
       <c r="B107" s="1"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:4">
       <c r="D112" s="2"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:2">
       <c r="B120" s="1"/>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:2">
       <c r="B125" s="1"/>
     </row>
   </sheetData>
@@ -1891,18 +1894,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BB6F14-E3DE-4AC5-A422-D5C8F6CDB5C6}">
   <dimension ref="A1:F125"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="9.35546875" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.265625" customWidth="1"/>
-    <col min="5" max="5" width="3.59765625" customWidth="1"/>
-    <col min="6" max="6" width="12.73046875" customWidth="1"/>
-    <col min="7" max="7" width="13.59765625" customWidth="1"/>
+    <col min="3" max="3" width="16.640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.28515625" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1916,7 +1919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
         <v>39</v>
       </c>
@@ -1924,7 +1927,7 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1935,7 +1938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" s="19" t="str">
         <f>DEC2HEX(HEX2DEC(A3)+4,8)</f>
         <v>000B0504</v>
@@ -1950,7 +1953,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" s="19" t="str">
         <f t="shared" ref="A5:A58" si="0">DEC2HEX(HEX2DEC(A4)+4,8)</f>
         <v>000B0508</v>
@@ -1963,7 +1966,7 @@
       </c>
       <c r="D5" s="19"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" s="19" t="str">
         <f t="shared" si="0"/>
         <v>000B050C</v>
@@ -1980,7 +1983,7 @@
         <v>030051E30040A0E11000000A</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>000B0510</v>
@@ -1995,7 +1998,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="A8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>000B0514</v>
@@ -2008,7 +2011,7 @@
       </c>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6">
       <c r="A9" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0518</v>
@@ -2023,7 +2026,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6">
       <c r="A10" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B051C</v>
@@ -2036,7 +2039,7 @@
       </c>
       <c r="D10" s="15"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6">
       <c r="A11" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0520</v>
@@ -2049,7 +2052,7 @@
       </c>
       <c r="D11" s="15"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6">
       <c r="A12" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0524</v>
@@ -2062,7 +2065,7 @@
       </c>
       <c r="D12" s="15"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6">
       <c r="A13" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0528</v>
@@ -2075,7 +2078,7 @@
       </c>
       <c r="D13" s="15"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6">
       <c r="A14" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B052C</v>
@@ -2088,7 +2091,7 @@
       </c>
       <c r="D14" s="15"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6">
       <c r="A15" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0530</v>
@@ -2102,7 +2105,7 @@
       <c r="D15" s="15"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6">
       <c r="A16" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0534</v>
@@ -2115,7 +2118,7 @@
       </c>
       <c r="D16" s="15"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6">
       <c r="A17" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0538</v>
@@ -2128,7 +2131,7 @@
       </c>
       <c r="D17" s="15"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6">
       <c r="A18" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B053C</v>
@@ -2141,7 +2144,7 @@
       </c>
       <c r="D18" s="15"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6">
       <c r="A19" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0540</v>
@@ -2154,7 +2157,7 @@
       </c>
       <c r="D19" s="15"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6">
       <c r="A20" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0544</v>
@@ -2168,7 +2171,7 @@
       <c r="D20" s="16"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6">
       <c r="A21" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0548</v>
@@ -2181,7 +2184,7 @@
       </c>
       <c r="D21" s="16"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6">
       <c r="A22" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B054C</v>
@@ -2194,7 +2197,7 @@
       </c>
       <c r="D22" s="16"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6">
       <c r="A23" s="15" t="str">
         <f t="shared" si="0"/>
         <v>000B0550</v>
@@ -2207,7 +2210,7 @@
       </c>
       <c r="D23" s="16"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6">
       <c r="A24" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000B0554</v>
@@ -2222,7 +2225,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6">
       <c r="A25" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000B0558</v>
@@ -2235,7 +2238,7 @@
       </c>
       <c r="D25" s="5"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6">
       <c r="A26" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000B055C</v>
@@ -2248,7 +2251,7 @@
       </c>
       <c r="D26" s="5"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6">
       <c r="A27" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000B0560</v>
@@ -2261,7 +2264,7 @@
       </c>
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6">
       <c r="A28" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000B0564</v>
@@ -2274,7 +2277,7 @@
       </c>
       <c r="D28" s="5"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6">
       <c r="A29" s="6" t="str">
         <f t="shared" si="0"/>
         <v>000B0568</v>
@@ -2289,7 +2292,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6">
       <c r="A30" s="6" t="str">
         <f t="shared" si="0"/>
         <v>000B056C</v>
@@ -2302,7 +2305,7 @@
       </c>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6">
       <c r="A31" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0570</v>
@@ -2317,7 +2320,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6">
       <c r="A32" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0574</v>
@@ -2330,7 +2333,7 @@
       </c>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4">
       <c r="A33" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0578</v>
@@ -2343,7 +2346,7 @@
       </c>
       <c r="D33" s="13"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4">
       <c r="A34" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B057C</v>
@@ -2356,7 +2359,7 @@
       </c>
       <c r="D34" s="13"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4">
       <c r="A35" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0580</v>
@@ -2369,7 +2372,7 @@
       </c>
       <c r="D35" s="13"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4">
       <c r="A36" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0584</v>
@@ -2382,7 +2385,7 @@
       </c>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4">
       <c r="A37" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0588</v>
@@ -2395,7 +2398,7 @@
       </c>
       <c r="D37" s="13"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4">
       <c r="A38" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B058C</v>
@@ -2408,7 +2411,7 @@
       </c>
       <c r="D38" s="13"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4">
       <c r="A39" s="12" t="str">
         <f t="shared" si="0"/>
         <v>000B0590</v>
@@ -2421,18 +2424,18 @@
       </c>
       <c r="D39" s="13"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4">
       <c r="B40" s="2"/>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4">
       <c r="A41" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B41" s="3"/>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>71</v>
       </c>
@@ -2444,7 +2447,7 @@
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4">
       <c r="A43" t="str">
         <f t="shared" si="0"/>
         <v>0001FA28</v>
@@ -2459,7 +2462,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4">
       <c r="A44" t="str">
         <f t="shared" si="0"/>
         <v>0001FA2C</v>
@@ -2474,7 +2477,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4">
       <c r="A45" t="str">
         <f t="shared" si="0"/>
         <v>0001FA30</v>
@@ -2487,7 +2490,7 @@
       </c>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4">
       <c r="A46" t="str">
         <f t="shared" si="0"/>
         <v>0001FA34</v>
@@ -2502,7 +2505,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4">
       <c r="A47" s="8" t="str">
         <f t="shared" si="0"/>
         <v>0001FA38</v>
@@ -2517,7 +2520,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4">
       <c r="A48" s="8" t="str">
         <f t="shared" si="0"/>
         <v>0001FA3C</v>
@@ -2530,7 +2533,7 @@
       </c>
       <c r="D48" s="22"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4">
       <c r="A49" s="8" t="str">
         <f t="shared" si="0"/>
         <v>0001FA40</v>
@@ -2543,7 +2546,7 @@
       </c>
       <c r="D49" s="22"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4">
       <c r="A50" s="19" t="str">
         <f t="shared" si="0"/>
         <v>0001FA44</v>
@@ -2558,7 +2561,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4">
       <c r="A51" s="19" t="str">
         <f t="shared" si="0"/>
         <v>0001FA48</v>
@@ -2571,7 +2574,7 @@
       </c>
       <c r="D51" s="24"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4">
       <c r="A52" s="19" t="str">
         <f t="shared" si="0"/>
         <v>0001FA4C</v>
@@ -2584,7 +2587,7 @@
       </c>
       <c r="D52" s="24"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4">
       <c r="A53" s="15" t="str">
         <f t="shared" si="0"/>
         <v>0001FA50</v>
@@ -2599,7 +2602,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4">
       <c r="A54" s="15" t="str">
         <f t="shared" si="0"/>
         <v>0001FA54</v>
@@ -2612,7 +2615,7 @@
       </c>
       <c r="D54" s="17"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4">
       <c r="A55" t="str">
         <f t="shared" si="0"/>
         <v>0001FA58</v>
@@ -2627,7 +2630,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4">
       <c r="A56" t="str">
         <f t="shared" si="0"/>
         <v>0001FA5C</v>
@@ -2642,7 +2645,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4">
       <c r="A57" t="str">
         <f t="shared" si="0"/>
         <v>0001FA60</v>
@@ -2657,7 +2660,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4">
       <c r="A58" t="str">
         <f t="shared" si="0"/>
         <v>0001FA64</v>
@@ -2672,127 +2675,127 @@
         <v>102</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4">
       <c r="B59" s="2"/>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4">
       <c r="B60" s="2"/>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4">
       <c r="B61" s="2"/>
       <c r="D61" s="2"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4">
       <c r="B62" s="2"/>
       <c r="D62" s="2"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:4">
       <c r="B63" s="2"/>
       <c r="D63" s="2"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:4">
       <c r="B64" s="3"/>
       <c r="D64" s="2"/>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:4">
       <c r="B65" s="2"/>
       <c r="D65" s="2"/>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:4">
       <c r="B66" s="2"/>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:4">
       <c r="B67" s="3"/>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:4">
       <c r="B68" s="2"/>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:4">
       <c r="B69" s="3"/>
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:4">
       <c r="B70" s="3"/>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:4">
       <c r="B71" s="2"/>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:4">
       <c r="B72" s="3"/>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:4">
       <c r="B73" s="2"/>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:4">
       <c r="B74" s="2"/>
       <c r="D74" s="3"/>
     </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:4">
       <c r="B75" s="2"/>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:4">
       <c r="B76" s="2"/>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:4">
       <c r="B77" s="2"/>
       <c r="D77" s="2"/>
     </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:4">
       <c r="B78" s="2"/>
       <c r="D78" s="2"/>
     </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:4">
       <c r="B79" s="2"/>
       <c r="D79" s="2"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:2">
       <c r="B81" s="1"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:2">
       <c r="B86" s="1"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:2">
       <c r="B88" s="1"/>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:2">
       <c r="B91" s="1"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:2">
       <c r="B92" s="1"/>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:2">
       <c r="B93" s="1"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:4">
       <c r="B98" s="1"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:4">
       <c r="B102" s="1"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:4">
       <c r="B106" s="1"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:4">
       <c r="A107" s="4"/>
       <c r="B107" s="1"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:4">
       <c r="D112" s="2"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:2">
       <c r="B120" s="1"/>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:2">
       <c r="B125" s="1"/>
     </row>
   </sheetData>
